--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,47 +1142,54 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24791</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>148</v>
       </c>
       <c r="L12" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2025</v>
+        <v>20242025</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1191,61 +1198,866 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Super Cup</t>
+          <t>LaLiga</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45527.6875</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42714</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>148</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stage Front Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>148</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>148</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>148</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>148</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>148</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>148</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>148</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Mallorca</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>148</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>148</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>148</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>148</v>
+      </c>
+      <c r="L25" t="n">
         <v>1484</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N25" t="n">
         <v>2025</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Super Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>148</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1484</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Super Cup</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,54 +1268,47 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23516</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>148</v>
       </c>
       <c r="L14" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>20242025</v>
+        <v>2025</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1324,18 +1317,18 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Super Cup</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -1343,35 +1336,35 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>148</v>
       </c>
       <c r="L15" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>20242025</v>
+        <v>2025</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1379,685 +1372,6 @@
         </is>
       </c>
       <c r="P15" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stage Front Stadium
- (Cornella de Llobregat)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>148</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Coliseum
- (Getafe)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>148</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Estadio Santiago Bernabéu
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>148</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.58333333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Estadio Municipal de Butarque
- (Leganes)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>12454</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>148</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45529.59375</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Alaves</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>148</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45529.6875</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Atl. Madrid</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>148</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45530.6875</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Estadio de la Ceramica
- (Villarreal)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>148</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45531.58333333334</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Estadi Mallorca Son Moix
- (Palma de Mallorca)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>148</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45531.6875</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Campo de Futbol de Vallecas
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>14505</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>148</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>148</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1484</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>148</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1484</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
         <is>
           <t>Super Cup</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,47 +1268,54 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45528.5</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>148</v>
       </c>
       <c r="L14" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2025</v>
+        <v>20242025</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1317,18 +1324,18 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Super Cup</t>
+          <t>LaLiga</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -1336,42 +1343,469 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stage Front Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>148</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>148</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>148</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>148</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>148</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>148</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1484</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Super Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Mallorca</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>148</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K22" t="n">
+        <v>148</v>
+      </c>
+      <c r="L22" t="n">
         <v>1484</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N22" t="n">
         <v>2025</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Super Cup</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2336,118 +2336,6 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>148</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1484</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2025</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>148</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1484</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2025</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,270 +512,1467 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vega A. C.
+          <t>Garcia V.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>148</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bengoetxea R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>148</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Busquets Ferrer M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>148</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>148</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>148</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>148</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>148</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>148</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>148</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>148</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>148</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stage Front Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>148</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>148</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>148</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>148</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Estadio El Sadar
  (Pamplona)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E21" t="n">
         <v>23516</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>ETdxjU8a</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Osasuna</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>148</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>WhAFMMRi</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Gil Manzano J.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>55926</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>148</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Lopez M.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stage Front Stadium
- (Cornella de Llobregat)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>148</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Rojas J. A.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>148</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>148</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45536.59375</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Coliseum
  (Getafe)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E23" t="n">
         <v>16500</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>dboeiWOt</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Getafe</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>148</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>148</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45536.6875</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>148</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ortiz M.
+          <t>Fuertes P.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio de la Ceramica
- (Villarreal)</t>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23000</v>
+        <v>53331</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ruiz A.
+          <t>Quintero A.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadi Mallorca Son Moix
- (Palma de Mallorca)</t>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26020</v>
+        <v>27618</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45531.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Grado C. S.
+          <t>Bengoetxea R.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Campo de Futbol de Vallecas
+          <t>Metropolitano Stadium
  (Madrid)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14505</v>
+        <v>70460</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,318 +716,308 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45532.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fuertes P.
+          <t>Sanchez J.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>148</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Maeso F.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>148</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Busquets Ferrer M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>148</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Estadio San Mamés
  (Bilbao)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E9" t="n">
         <v>53331</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>148</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>f92vnwe3</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45532.58333333334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Quintero A.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Estadio José Zorrilla
- (Valladolid)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>148</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45532.6875</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bengoetxea R.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Atl. Madrid</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>148</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45532.6875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sanchez J.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Reale Arena
- (San Sebastian)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Alaves</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>148</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45533.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Maeso F.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Estadio Municipal de Montilivi
- (Girona)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>14624</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1056,46 +1046,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45533.6875</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Busquets Ferrer M.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45535.59375</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estadio de Gran Canaria
- (Las Palmas)</t>
+          <t>Stage Front Stadium
+ (Cornella de Llobregat)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32392</v>
+        <v>40000</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1124,41 +1109,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>55926</v>
+        <v>12454</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1187,41 +1172,41 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53331</v>
+        <v>49430</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1250,41 +1235,41 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.5</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stage Front Stadium
- (Cornella de Llobregat)</t>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>40000</v>
+        <v>19840</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1313,41 +1298,41 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque
- (Leganes)</t>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12454</v>
+        <v>23516</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1376,41 +1361,41 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Estadio de Mestalla
- (Valencia)</t>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49430</v>
+        <v>42714</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1439,41 +1424,41 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.59375</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19840</v>
+        <v>16500</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1502,41 +1487,41 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.6875</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>23516</v>
+        <v>83186</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1557,195 +1542,6 @@
         </is>
       </c>
       <c r="P17" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Estadio Ramón Sánchez Pizjuán
- (Sevilla)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>148</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Coliseum
- (Getafe)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>148</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Estadio Santiago Bernabéu
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>148</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fuertes P.
+          <t>Diaz de Mera I.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53331</v>
+        <v>55926</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Quintero A.
+          <t>Hernandez A.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio José Zorrilla
- (Valladolid)</t>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27618</v>
+        <v>53331</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.59375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bengoetxea R.
+          <t>Vega A. C.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
+          <t>Stage Front Stadium
+ (Cornella de Llobregat)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70460</v>
+        <v>40000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sanchez J.
+          <t>Lopez M.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reale Arena
- (San Sebastian)</t>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>12454</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maeso F.
+          <t>Gil Manzano J.
  (Esp)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Montilivi
- (Girona)</t>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14624</v>
+        <v>49430</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,46 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Busquets Ferrer M.
+          <t>Garcia V.
  (Esp)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Estadio de Gran Canaria
- (Las Palmas)</t>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32392</v>
+        <v>19840</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>IyRQC2vM</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -920,41 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45536.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55926</v>
+        <v>23516</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -983,41 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sanchez J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53331</v>
+        <v>42714</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1046,41 +1056,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.59375</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45536.59375</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munuera Montero J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stage Front Stadium
- (Cornella de Llobregat)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>40000</v>
+        <v>16500</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1109,41 +1124,46 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.6875</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>45536.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rojas J. A.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque
- (Leganes)</t>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12454</v>
+        <v>83186</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1164,384 +1184,6 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45535.6875</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla
- (Valencia)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>148</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Alaves</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>148</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>148</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Estadio Ramón Sánchez Pizjuán
- (Sevilla)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>148</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Coliseum
- (Getafe)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>148</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Estadio Santiago Bernabéu
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>148</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Diaz de Mera I.
+          <t>Garcia V.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>55926</v>
+        <v>19840</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hernandez A.
+          <t>Munuera J.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53331</v>
+        <v>23516</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vega A. C.
+          <t>Sanchez J.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stage Front Stadium
- (Cornella de Llobregat)</t>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40000</v>
+        <v>42714</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.59375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lopez M.
+          <t>Munuera Montero J.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque
- (Leganes)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12454</v>
+        <v>16500</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gil Manzano J.
+          <t>Rojas J. A.
  (Esp)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio de Mestalla
- (Valencia)</t>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49430</v>
+        <v>83186</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -844,346 +844,6 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Garcia V.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Alaves</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>148</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munuera J.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>148</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sanchez J.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Estadio Ramón Sánchez Pizjuán
- (Sevilla)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>148</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munuera Montero J.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Coliseum
- (Getafe)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>148</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rojas J. A.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Estadio Santiago Bernabéu
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>148</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YeqTho8m</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Garcia V.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45548.66666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19840</v>
+        <v>60721</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>08zpk37C</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munuera J.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45549.375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23516</v>
+        <v>26020</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sanchez J.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45549.46875</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán
- (Sevilla)</t>
+          <t>Stage Front Stadium
+ (Cornella de Llobregat)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42714</v>
+        <v>40000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>8EcB5Oig</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munuera Montero J.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45549.5625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Coliseum
- (Getafe)</t>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16500</v>
+        <v>42714</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>dboeiWOt</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Getafe</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Rojas J. A.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio Santiago Bernabéu
- (Madrid)</t>
+          <t>Reale Arena
+ (San Sebastian)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>83186</v>
+        <v>40000</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Betis</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -844,6 +819,321 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>148</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.46875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>148</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>148</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,1014 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45552.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>148</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45553.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45554.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>148</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45555.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>148</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.46875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>148</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>148</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>148</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>148</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45557.46875</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>148</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45557.5625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>148</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45557.66666666666</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>148</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>148</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>148</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>148</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>148</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,401 +512,1966 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.375</v>
+        <v>45552.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>Vega A. C.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>148</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45553.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pulido J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>148</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45554.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Maeso F.
  (Esp)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>148</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45555.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>148</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>148</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.46875</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>148</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>148</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.375</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>148</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45557.46875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45557.5625</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>148</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45557.66666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>148</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>148</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>148</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45560.58333333334</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>148</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45560.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>148</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RCDE Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>148</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>148</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Estadio de Balaídos
  (Vigo)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E22" t="n">
         <v>24791</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>8pvUZFhf</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Celta Vigo</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>148</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>zkpajjvm</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Valladolid</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>148</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>na927pNt</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.46875</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ruiz A.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Estadio Municipal de Montilivi
- (Girona)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>14624</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>148</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>148</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>148</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>148</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>148</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45564.375</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>nNNpcUSL</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Girona</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>148</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.5625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ortiz M.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Estadio de Gran Canaria
- (Las Palmas)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>32392</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="K28" t="n">
+        <v>148</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>IP5zl0cJ</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Ath Bilbao</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>148</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Grado C. S.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>148</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>148</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45564.66666666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Metropolitano Stadium
  (Madrid)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E31" t="n">
         <v>70460</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>jaarqpLQ</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Atl. Madrid</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>148</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45551.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Quintero A.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Campo de Futbol de Vallecas
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14505</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>148</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45552.58333333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Estadi Mallorca Son Moix
- (Palma de Mallorca)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>148</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>148</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>148</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,401 +512,1830 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.375</v>
+        <v>45558.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Maeso F.
+          <t>Garcia V.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>148</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>148</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>148</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>148</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45560.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>148</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45560.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>148</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RCDE Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>148</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Estadio de Balaídos
  (Vigo)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E10" t="n">
         <v>24791</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>8pvUZFhf</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Celta Vigo</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>148</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>zkpajjvm</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Valladolid</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>148</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>na927pNt</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.46875</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ruiz A.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>148</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>148</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>148</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>148</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>148</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>148</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>148</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45569.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>148</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45570.375</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RCDE Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>148</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45570.46875</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>148</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>148</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>148</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>148</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45571.375</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Estadio Municipal de Montilivi
  (Girona)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E27" t="n">
         <v>14624</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>nNNpcUSL</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Girona</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>148</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45571.46875</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>148</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.5625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ortiz M.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Estadio de Gran Canaria
- (Las Palmas)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>32392</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>148</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Grado C. S.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="K28" t="n">
+        <v>148</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45571.5625</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>148</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45571.66666666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>jaarqpLQ</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Atl. Madrid</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>148</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45551.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Quintero A.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Campo de Futbol de Vallecas
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14505</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>148</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45552.58333333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Estadi Mallorca Son Moix
- (Palma de Mallorca)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>148</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="K30" t="n">
+        <v>148</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Munuera Montero J.
+          <t>Bengoetxea R.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio José Zorrilla
- (Valladolid)</t>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27618</v>
+        <v>24791</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.375</v>
+        <v>45564.46875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Diaz de Mera I.
+          <t>Grado C. S.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Coliseum
- (Getafe)</t>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16500</v>
+        <v>53331</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.46875</v>
+        <v>45564.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ruiz A.
+          <t>Hernandez A.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Campo de Futbol de Vallecas
- (Madrid)</t>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14505</v>
+        <v>60721</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.5625</v>
+        <v>45564.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rojas J. A.
+          <t>Busquets Ferrer M.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reale Arena
- (San Sebastian)</t>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>70460</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cuadra G.
+          <t>Lopez M.
  (Esp)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23516</v>
+        <v>23000</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -844,278 +844,6 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bengoetxea R.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Estadio de Balaídos
- (Vigo)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>148</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.46875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Grado C. S.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>148</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Hernandez A.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Estadio Benito Villamarín
- (Sevilla)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>60721</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>148</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.66666666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Busquets Ferrer M.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Atl. Madrid</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>148</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.375</v>
+        <v>45569.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bengoetxea R.
+          <t>Quintero A.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio de Balaídos
- (Vigo)</t>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24791</v>
+        <v>12454</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.46875</v>
+        <v>45570.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Grado C. S.
+          <t>Maeso F.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
+          <t>RCDE Stadium
+ (Cornella de Llobregat)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53331</v>
+        <v>40000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5625</v>
+        <v>45570.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hernandez A.
+          <t>Sanchez J.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estadio Benito Villamarín
- (Sevilla)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60721</v>
+        <v>16500</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Busquets Ferrer M.
+          <t>Vega A. C.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70460</v>
+        <v>32392</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lopez M.
+          <t>Fuertes P.
  (Esp)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio de la Ceramica
- (Villarreal)</t>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23000</v>
+        <v>27618</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -844,6 +844,535 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cuadra G.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>148</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pulido J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.46875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ortiz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>148</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>148</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Diaz de Mera I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45583.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>148</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.46875</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>148</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.66666666666</v>
+        <v>45571.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Quintero A.
+          <t>Pulido J.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque
- (Leganes)</t>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12454</v>
+        <v>14624</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.375</v>
+        <v>45571.46875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maeso F.
+          <t>Ortiz M.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RCDE Stadium
- (Cornella de Llobregat)</t>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40000</v>
+        <v>19840</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.46875</v>
+        <v>45571.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sanchez J.
+          <t>Munuera J.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Coliseum
- (Getafe)</t>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16500</v>
+        <v>42714</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45571.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vega A. C.
+          <t>Diaz de Mera I.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estadio de Gran Canaria
- (Las Palmas)</t>
+          <t>Reale Arena
+ (San Sebastian)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32392</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fuertes P.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45583.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio José Zorrilla
- (Valladolid)</t>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27618</v>
+        <v>19840</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>zkpajjvm</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,46 +847,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.66666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cuadra G.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45584.375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Estadio Santiago Bernabéu
- (Madrid)</t>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>83186</v>
+        <v>53331</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -920,46 +910,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.375</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pulido J.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45584.46875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Montilivi
- (Girona)</t>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14624</v>
+        <v>23516</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -988,46 +973,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.46875</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ortiz M.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45584.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19840</v>
+        <v>14624</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1056,46 +1036,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.5625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munuera J.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán
- (Sevilla)</t>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>42714</v>
+        <v>24791</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1124,46 +1099,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.66666666666</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Diaz de Mera I.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45585.375</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reale Arena
- (San Sebastian)</t>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40000</v>
+        <v>26020</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1192,41 +1162,41 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45585.46875</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19840</v>
+        <v>70460</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1255,41 +1225,41 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.375</v>
+        <v>45585.5625</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53331</v>
+        <v>23000</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1318,41 +1288,41 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>23516</v>
+        <v>55926</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K14" t="n">

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45583.66666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lopez M.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Estadio Mendizorrotza
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45584.375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Busquets Ferrer M.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Estadio San Mamés
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45584.46875</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ruiz A.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Estadio El Sadar
@@ -707,7 +722,12 @@
       <c r="B5" s="2" t="n">
         <v>45584.5625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Grado C. S.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Estadio Municipal de Montilivi
@@ -770,7 +790,12 @@
       <c r="B6" s="2" t="n">
         <v>45584.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hernandez A.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Estadio de Balaídos
@@ -833,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45585.375</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rojas J. A.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Estadi Mallorca Son Moix
@@ -896,7 +926,12 @@
       <c r="B8" s="2" t="n">
         <v>45585.46875</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munuera Montero J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Metropolitano Stadium
@@ -959,7 +994,12 @@
       <c r="B9" s="2" t="n">
         <v>45585.5625</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Garcia V.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Estadio de la Ceramica
@@ -1022,7 +1062,12 @@
       <c r="B10" s="2" t="n">
         <v>45585.66666666666</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bengoetxea R.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Estadi Olímpic Lluís Companys
@@ -1085,7 +1130,12 @@
       <c r="B11" s="2" t="n">
         <v>45586.66666666666</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Estadio de Mestalla

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,338 +512,1258 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Rojas J. A.
- (Esp)</t>
-        </is>
-      </c>
+        <v>45590.66666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>RCDE Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>148</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45591.375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>148</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.46875</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>14708</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>148</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>148</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>148</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>148</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.51041666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.60416666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>148</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.70833333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>148</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45593.70833333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Estadi Mallorca Son Moix
  (Palma de Mallorca)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E11" t="n">
         <v>26020</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Mallorca</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>148</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.51041666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>148</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>8bcjFy6O</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Rayo Vallecano</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>148</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.46875</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munuera Montero J.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="K15" t="n">
+        <v>148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>148</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.41666666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Metropolitano Stadium
  (Madrid)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E17" t="n">
         <v>70460</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>jaarqpLQ</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Atl. Madrid</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>148</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45585.5625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Garcia V.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Estadio de la Ceramica
- (Villarreal)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>148</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45585.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bengoetxea R.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>148</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.51041666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Estadi Olímpic Lluís Companys
  (Barcelona)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E18" t="n">
         <v>55926</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>148</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>h8oAv4Ts</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>148</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>QqTA4cPk</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45586.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Gil Manzano J.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla
- (Valencia)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>148</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>148</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45599.70833333334</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>148</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.70833333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>148</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45590.66666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ortiz M.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>RCDE Stadium
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45591.375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Maeso F.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Estadio José Zorrilla
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45591.46875</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Vega A. C.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Campo de Futbol de Vallecas
@@ -707,7 +722,12 @@
       <c r="B5" s="2" t="n">
         <v>45591.5625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Quintero A.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Estadio de Gran Canaria
@@ -770,7 +790,12 @@
       <c r="B6" s="2" t="n">
         <v>45591.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sanchez J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Estadio Santiago Bernabéu
@@ -833,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45592.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lopez M.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Estadio Municipal de Butarque
@@ -896,7 +926,12 @@
       <c r="B8" s="2" t="n">
         <v>45592.51041666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cuadra G.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Coliseum
@@ -959,7 +994,12 @@
       <c r="B9" s="2" t="n">
         <v>45592.60416666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Estadio Benito Villamarín
@@ -1022,7 +1062,12 @@
       <c r="B10" s="2" t="n">
         <v>45592.70833333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pulido J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Reale Arena
@@ -1085,7 +1130,12 @@
       <c r="B11" s="2" t="n">
         <v>45593.70833333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Estadi Mallorca Son Moix
@@ -1134,636 +1184,6 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45597.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Alaves</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>148</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>148</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.51041666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Estadio Municipal de Montilivi
- (Girona)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>14624</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>148</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Estadio de la Ceramica
- (Villarreal)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>148</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.70833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Estadio de Mestalla
- (Valencia)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>148</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45599.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Atl. Madrid</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>148</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.51041666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>55926</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>148</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Estadio Ramón Sánchez Pizjuán
- (Sevilla)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>148</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45599.70833333334</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>148</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Estadio de Balaídos
- (Vigo)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>148</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,41 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45599.41666666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estadio de la Ceramica
- (Villarreal)</t>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23000</v>
+        <v>70460</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45599.51041666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio de Mestalla
- (Valencia)</t>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49430</v>
+        <v>55926</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +827,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.41666666666</v>
+        <v>45599.60416666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70460</v>
+        <v>42714</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +890,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.51041666666</v>
+        <v>45599.70833333334</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55926</v>
+        <v>53331</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +953,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.60416666666</v>
+        <v>45600.70833333334</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán
- (Sevilla)</t>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42714</v>
+        <v>24791</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1008,762 +1008,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45599.70833333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>148</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Estadio de Balaídos
- (Vigo)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>148</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45604.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Campo de Futbol de Vallecas
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>14708</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>148</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Estadio Santiago Bernabéu
- (Madrid)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>148</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bXuieB8c</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.51041666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Estadio de la Ceramica
- (Villarreal)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Alaves</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>148</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RCDE Stadium
- (Cornella de Llobregat)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>148</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Coliseum
- (Getafe)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>148</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Estadio Benito Villamarín
- (Sevilla)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>60721</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>148</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Ia5ItCg4</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.51041666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Estadi Mallorca Son Moix
- (Palma de Mallorca)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Atl. Madrid</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>148</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Estadio Municipal de Butarque
- (Leganes)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>12454</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>148</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Estadio José Zorrilla
- (Valladolid)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Ath Bilbao</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>148</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45606.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Reale Arena
- (San Sebastian)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>148</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,41 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45604.70833333334</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19840</v>
+        <v>14708</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.41666666666</v>
+        <v>45605.41666666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio El Sadar
- (Pamplona)</t>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23516</v>
+        <v>83186</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>ETdxjU8a</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.51041666666</v>
+        <v>45605.51041666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Montilivi
- (Girona)</t>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14624</v>
+        <v>23000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.41666666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metropolitano Stadium
- (Madrid)</t>
+          <t>RCDE Stadium
+ (Cornella de Llobregat)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70460</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.51041666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>55926</v>
+        <v>12454</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +827,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.60416666666</v>
+        <v>45606.41666666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán
+          <t>Estadio Benito Villamarín
  (Sevilla)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42714</v>
+        <v>60721</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +890,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.70833333334</v>
+        <v>45606.51041666666</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53331</v>
+        <v>26020</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +953,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45600.70833333334</v>
+        <v>45606.60416666666</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Estadio de Balaídos
- (Vigo)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24791</v>
+        <v>16500</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1008,6 +1008,132 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>148</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/spain/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45604.70833333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Maeso F.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Campo de Futbol de Vallecas
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45605.41666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lopez M.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Estadio Santiago Bernabéu
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45605.51041666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Quintero A.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Estadio de la Ceramica
@@ -701,41 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pulido J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RCDE Stadium
- (Cornella de Llobregat)</t>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>12454</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45606.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ortiz M.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque
- (Leganes)</t>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12454</v>
+        <v>60721</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45606.41666666666</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45606.51041666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sanchez J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Estadio Benito Villamarín
- (Sevilla)</t>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60721</v>
+        <v>26020</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45606.51041666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Estadi Mallorca Son Moix
- (Palma de Mallorca)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26020</v>
+        <v>16500</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>45606.60416666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vega A. C.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Coliseum
- (Getafe)</t>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16500</v>
+        <v>27618</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Ath Bilbao</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1016,41 +1056,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cuadra G.
+ (Esp)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estadio José Zorrilla
- (Valladolid)</t>
+          <t>Reale Arena
+ (San Sebastian)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27618</v>
+        <v>40000</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1079,41 +1124,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45606.70833333334</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reale Arena
- (San Sebastian)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40000</v>
+        <v>16500</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1134,6 +1179,258 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>148</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.51041666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>148</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>148</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>LaLiga</t>
         </is>
